--- a/24_Distressed_Restructuring/_template_RESTRUCTURING.xlsx
+++ b/24_Distressed_Restructuring/_template_RESTRUCTURING.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t xml:space="preserve">[COMPANY] — Distressed / Restructuring Model</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t xml:space="preserve">Fulcrum security = the tranche where recovery % first drops below 100% — that class controls the reorg (converts to new equity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fulcrum security</t>
   </si>
   <si>
     <t xml:space="preserve">Liquidation (Ch. 7) vs. Reorganization (Ch. 11) NPV</t>
@@ -304,7 +307,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -342,6 +345,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -626,7 +633,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -687,8 +694,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:G20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A2:G21"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
@@ -740,6 +747,10 @@
         <f aca="false">IFERROR(E5/C5,"-")</f>
         <v>-</v>
       </c>
+      <c r="G5" s="10" t="str">
+        <f aca="false">IF(AND(ISNUMBER(F5),F5&lt;1),"FULCRUM","")</f>
+        <v/>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
@@ -759,6 +770,10 @@
         <f aca="false">IFERROR(E6/C6,"-")</f>
         <v>-</v>
       </c>
+      <c r="G6" s="10" t="str">
+        <f aca="false">IF(AND(ISNUMBER(F6),F6&lt;1,ISNUMBER(F5),F5&gt;=1),"FULCRUM","")</f>
+        <v/>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
@@ -778,6 +793,10 @@
         <f aca="false">IFERROR(E7/C7,"-")</f>
         <v>-</v>
       </c>
+      <c r="G7" s="10" t="str">
+        <f aca="false">IF(AND(ISNUMBER(F7),F7&lt;1,ISNUMBER(F6),F6&gt;=1),"FULCRUM","")</f>
+        <v/>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
@@ -797,6 +816,10 @@
         <f aca="false">IFERROR(E8/C8,"-")</f>
         <v>-</v>
       </c>
+      <c r="G8" s="10" t="str">
+        <f aca="false">IF(AND(ISNUMBER(F8),F8&lt;1,ISNUMBER(F7),F7&gt;=1),"FULCRUM","")</f>
+        <v/>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
@@ -816,6 +839,10 @@
         <f aca="false">IFERROR(E9/C9,"-")</f>
         <v>-</v>
       </c>
+      <c r="G9" s="10" t="str">
+        <f aca="false">IF(AND(ISNUMBER(F9),F9&lt;1,ISNUMBER(F8),F8&gt;=1),"FULCRUM","")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
@@ -835,23 +862,36 @@
         <f aca="false">IFERROR(E10/C10,"-")</f>
         <v>-</v>
       </c>
+      <c r="G10" s="10" t="str">
+        <f aca="false">IF(AND(ISNUMBER(F10),F10&lt;1,ISNUMBER(F9),F9&gt;=1),"FULCRUM","")</f>
+        <v/>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="13" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="10" t="str">
+        <f aca="false">IFERROR(INDEX(B5:B10,MATCH("FULCRUM",G5:G10,0)),"-")</f>
+        <v>-</v>
       </c>
     </row>
   </sheetData>
@@ -871,7 +911,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -881,23 +921,23 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>0</v>
@@ -908,16 +948,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="13"/>
+      <c r="D6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>0</v>
@@ -928,31 +968,31 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="C8" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="C9" s="16" t="n">
         <v>0.15</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">C5-C6-C7</f>
@@ -965,18 +1005,18 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="C12" s="17" t="n">
         <f aca="false">C11/(1+$C$9)^(C8/12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <f aca="false">D11/(1+$C$9)^(D8/12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>35</v>
+      <c r="E12" s="13" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +1036,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
@@ -1007,95 +1047,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
